--- a/SGC-CKN/Excel/932e33ed-1d89-466e-a5c1-2bde695f7d33_Thanh_Hoá_P1-55_D800_21-04-2026.xlsx
+++ b/SGC-CKN/Excel/932e33ed-1d89-466e-a5c1-2bde695f7d33_Thanh_Hoá_P1-55_D800_21-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>04:30 21/04/2026</t>
+    <t>04:30 02/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:16 21/04/2026</t>
+    <t>14:16 02/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">04:30
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:40
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:05
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">06:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:03
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:15
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:40
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,7 +176,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:16
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>chạm sỏi, kết thúc khoan</t>

--- a/SGC-CKN/Excel/932e33ed-1d89-466e-a5c1-2bde695f7d33_Thanh_Hoá_P1-55_D800_21-04-2026.xlsx
+++ b/SGC-CKN/Excel/932e33ed-1d89-466e-a5c1-2bde695f7d33_Thanh_Hoá_P1-55_D800_21-04-2026.xlsx
@@ -1396,13 +1396,13 @@
         <v>-39.1</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.4</v>
+        <v>-44.41</v>
       </c>
       <c r="H18" s="28">
         <v>2.6</v>
       </c>
       <c r="I18" s="28">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="J18" s="15">
         <v>2.04</v>
@@ -1766,13 +1766,13 @@
         <v>-39.1</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.4</v>
+        <v>-44.41</v>
       </c>
       <c r="G9" s="28">
         <v>2.6</v>
       </c>
       <c r="H9" s="28">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="I9" s="15">
         <v>2.04</v>
@@ -1795,13 +1795,13 @@
         <v>-0.84</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.4</v>
+        <v>-44.41</v>
       </c>
       <c r="G10" s="33">
         <v>9.77</v>
       </c>
       <c r="H10" s="33">
-        <v>43.56</v>
+        <v>43.57</v>
       </c>
       <c r="I10" s="33">
         <v>4.46</v>
